--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/DISTRICT_OF_COLUMBIA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/DISTRICT_OF_COLUMBIA_2011.xlsx
@@ -463,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>0.009933774834437</v>
+        <v>0.009933774834437002</v>
       </c>
     </row>
     <row r="7">
@@ -481,7 +481,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0.009933774834437</v>
+        <v>0.009933774834437002</v>
       </c>
     </row>
     <row r="8">
@@ -1003,7 +1003,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>0.009933774834437</v>
+        <v>0.009933774834437002</v>
       </c>
     </row>
     <row r="37">
@@ -1093,7 +1093,7 @@
         <v>3</v>
       </c>
       <c r="D41">
-        <v>0.009933774834437</v>
+        <v>0.009933774834437002</v>
       </c>
     </row>
     <row r="42">
@@ -2353,7 +2353,7 @@
         <v>3</v>
       </c>
       <c r="D111">
-        <v>0.009933774834437</v>
+        <v>0.009933774834437002</v>
       </c>
     </row>
     <row r="112">
